--- a/scorecard.xlsx
+++ b/scorecard.xlsx
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>In force — Law No. 2004-63 on Data Protection</t>
+          <t>In force — Law No. 2004-63 on Data Protection (2004), amendments under consideration</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>In force (Law No. 2010/012 on Cybersecurity and Cybercrime)</t>
+          <t>In force — Law No. 2010/012 on Cybersecurity and Cybercrime (2010), includes data protection provisions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>In force (Law No. 001/2011 on Personal Data Protection)</t>
+          <t>In force — Law No. 001/2011 on Personal Data Protection (2011), CNPDCP regulator</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Decriminalised (2019 recriminalisation repealed 2020)</t>
+          <t>Decriminalised — 2019 recriminalisation repealed 2020, no formal recognition</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.humandignitytrust.org/country-profile/gabon/; https://ilga.org/ilga-world-maps/</t>
+          <t>ILGA World Maps, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>In force (Law No. 2009-09 on Personal Data Protection)</t>
+          <t>In force — Law No. 2009-09 on Personal Data Protection (2009), APDP regulator active</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Draft/Early (AI policy referenced in Digital Strategy 2021)</t>
+          <t>Draft/Early — AI policy referenced in Digital Strategy 2021, no formal AI strategy adopted</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://en.unesco.org/artificial-intelligence/observatory/policies?country=BJ; https://www.unesco.org/ethics-ai/en/global-hub</t>
+          <t>UNESCO AI Policy Observatory, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>In force (Law No. 133/V/2001, updated 2013)</t>
+          <t>In force — Law No. 133/V/2001 on Personal Data Protection (2001, amended 2013, updated 2021)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Legal (same-sex relations decriminalised 2004; no recognition)</t>
+          <t>Legal — decriminalised 2004, anti-discrimination protections added 2008, no marriage recognition</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.humandignitytrust.org/country-profile/cabo-verde/; https://ilga.org/ilga-world-maps/</t>
+          <t>ILGA World Maps, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>In force — Law 2008-12 on Personal Data Protection</t>
+          <t>In force — Law 2008-12 on Personal Data Protection (2008), enforced by CDP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://unctad.org/page/data-protection-and-privacy-legislation-worldwide</t>
+          <t>UNCTAD Data Protection Tracker, accessed 2026-01-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
